--- a/Data/Resultados Consolidados.xlsx
+++ b/Data/Resultados Consolidados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Prospectiva/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="8_{5A0125F4-F39D-48F3-8432-D669FE6910DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EACFCDE6-D3FF-4B22-B906-64399C3A0E87}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="8_{5A0125F4-F39D-48F3-8432-D669FE6910DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{393D33C0-F778-4041-9072-995254D5C932}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{E2458CD7-6E56-4AAC-ADAB-972730991000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="213">
   <si>
     <t>Id</t>
   </si>
@@ -706,6 +706,9 @@
   </si>
   <si>
     <t>Meta_PDI</t>
+  </si>
+  <si>
+    <t>Porcentaje de cumplimiento del Acuerdo de Nivel de Servicio (ANS)</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1661,7 @@
         <v>193</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>13</v>
@@ -31650,14 +31653,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31896,29 +31897,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CBBBE0-1686-4AC4-9DEE-86E504F957B7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2341E7-1C26-47FA-8834-8CFE31E76839}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e1e4522-69aa-4722-84bc-71e77db393d9"/>
-    <ds:schemaRef ds:uri="db99feaa-0329-41d7-b368-b1960e46cf3e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31943,9 +31935,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2341E7-1C26-47FA-8834-8CFE31E76839}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CBBBE0-1686-4AC4-9DEE-86E504F957B7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e1e4522-69aa-4722-84bc-71e77db393d9"/>
+    <ds:schemaRef ds:uri="db99feaa-0329-41d7-b368-b1960e46cf3e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Data/Resultados Consolidados.xlsx
+++ b/Data/Resultados Consolidados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{5A0125F4-F39D-48F3-8432-D669FE6910DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{393D33C0-F778-4041-9072-995254D5C932}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="8_{5A0125F4-F39D-48F3-8432-D669FE6910DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFDB23ED-01B8-4DE3-9FD2-C57F3BE4DCF0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{E2458CD7-6E56-4AAC-ADAB-972730991000}"/>
   </bookViews>
@@ -31653,12 +31653,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31897,20 +31899,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2341E7-1C26-47FA-8834-8CFE31E76839}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CBBBE0-1686-4AC4-9DEE-86E504F957B7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e1e4522-69aa-4722-84bc-71e77db393d9"/>
+    <ds:schemaRef ds:uri="db99feaa-0329-41d7-b368-b1960e46cf3e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31935,20 +31946,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CBBBE0-1686-4AC4-9DEE-86E504F957B7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2341E7-1C26-47FA-8834-8CFE31E76839}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e1e4522-69aa-4722-84bc-71e77db393d9"/>
-    <ds:schemaRef ds:uri="db99feaa-0329-41d7-b368-b1960e46cf3e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Data/Resultados Consolidados.xlsx
+++ b/Data/Resultados Consolidados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="8_{5A0125F4-F39D-48F3-8432-D669FE6910DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFDB23ED-01B8-4DE3-9FD2-C57F3BE4DCF0}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="8_{5A0125F4-F39D-48F3-8432-D669FE6910DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C13E2B9-F9B9-4076-866D-0AE550D81E43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="692" xr2:uid="{E2458CD7-6E56-4AAC-ADAB-972730991000}"/>
   </bookViews>
@@ -1514,6 +1514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07F8AFD-5556-4E88-A2AA-EDDEBB18E2EB}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1574,7 +1575,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="44">
         <v>77</v>
       </c>
@@ -1615,7 +1616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="44">
         <v>148</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="44">
         <v>193</v>
       </c>
@@ -1697,7 +1698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44">
         <v>194</v>
       </c>
@@ -1738,7 +1739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="44">
         <v>200</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="44">
         <v>202</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="44">
         <v>203</v>
       </c>
@@ -1861,7 +1862,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="44">
         <v>204</v>
       </c>
@@ -1902,7 +1903,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="44">
         <v>205</v>
       </c>
@@ -1943,7 +1944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="44">
         <v>206</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="44">
         <v>207</v>
       </c>
@@ -2025,7 +2026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="44">
         <v>228</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="44">
         <v>244</v>
       </c>
@@ -2107,7 +2108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44">
         <v>245</v>
       </c>
@@ -2148,7 +2149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44">
         <v>274</v>
       </c>
@@ -2189,7 +2190,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="44">
         <v>276</v>
       </c>
@@ -2230,7 +2231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44">
         <v>277</v>
       </c>
@@ -2269,7 +2270,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44">
         <v>323</v>
       </c>
@@ -2310,7 +2311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44">
         <v>325</v>
       </c>
@@ -2351,7 +2352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44">
         <v>331</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44">
         <v>332</v>
       </c>
@@ -2433,7 +2434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44">
         <v>334</v>
       </c>
@@ -2474,7 +2475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44">
         <v>335</v>
       </c>
@@ -2513,7 +2514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44">
         <v>339</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="44">
         <v>353</v>
       </c>
@@ -2595,7 +2596,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="46" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" s="46" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44">
         <v>361</v>
       </c>
@@ -2636,7 +2637,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="44">
         <v>364</v>
       </c>
@@ -2677,7 +2678,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="46" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" s="46" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44">
         <v>367</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="44">
         <v>369</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="44">
         <v>376</v>
       </c>
@@ -2800,7 +2801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="44">
         <v>377</v>
       </c>
@@ -2841,7 +2842,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="44">
         <v>379</v>
       </c>
@@ -2882,7 +2883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="44">
         <v>385</v>
       </c>
@@ -2923,7 +2924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="44">
         <v>423</v>
       </c>
@@ -2964,7 +2965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="44">
         <v>424</v>
       </c>
@@ -3005,7 +3006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="44">
         <v>14</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="44" t="s">
         <v>80</v>
       </c>
@@ -3128,7 +3129,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="44" t="s">
         <v>82</v>
       </c>
@@ -3169,7 +3170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="44" t="s">
         <v>84</v>
       </c>
@@ -3210,7 +3211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="44" t="s">
         <v>86</v>
       </c>
@@ -3251,7 +3252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="44" t="s">
         <v>88</v>
       </c>
@@ -3292,7 +3293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="44" t="s">
         <v>89</v>
       </c>
@@ -3333,7 +3334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="44" t="s">
         <v>90</v>
       </c>
@@ -3374,7 +3375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="44">
         <v>97</v>
       </c>
@@ -3415,7 +3416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="44">
         <v>98</v>
       </c>
@@ -3456,7 +3457,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="44">
         <v>109</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="44">
         <v>460</v>
       </c>
@@ -3536,7 +3537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="44">
         <v>463</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="44">
         <v>465</v>
       </c>
@@ -3618,7 +3619,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="44">
         <v>466</v>
       </c>
@@ -3659,7 +3660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="44">
         <v>472</v>
       </c>
@@ -3698,7 +3699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="44">
         <v>476</v>
       </c>
@@ -3739,7 +3740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="44">
         <v>525</v>
       </c>
@@ -3776,7 +3777,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="44" t="s">
         <v>146</v>
       </c>
@@ -3813,7 +3814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="44" t="s">
         <v>148</v>
       </c>
@@ -3850,7 +3851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="44" t="s">
         <v>150</v>
       </c>
@@ -3889,6 +3890,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:M58" xr:uid="{F07F8AFD-5556-4E88-A2AA-EDDEBB18E2EB}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Productos de investigación, innovación y creación"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A39:A42">
     <cfRule type="duplicateValues" dxfId="18" priority="23"/>
   </conditionalFormatting>
@@ -31653,14 +31661,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31899,29 +31905,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CBBBE0-1686-4AC4-9DEE-86E504F957B7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2341E7-1C26-47FA-8834-8CFE31E76839}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e1e4522-69aa-4722-84bc-71e77db393d9"/>
-    <ds:schemaRef ds:uri="db99feaa-0329-41d7-b368-b1960e46cf3e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31946,9 +31943,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2341E7-1C26-47FA-8834-8CFE31E76839}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96CBBBE0-1686-4AC4-9DEE-86E504F957B7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e1e4522-69aa-4722-84bc-71e77db393d9"/>
+    <ds:schemaRef ds:uri="db99feaa-0329-41d7-b368-b1960e46cf3e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>